--- a/Windows桌面项目计划.xlsx
+++ b/Windows桌面项目计划.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目计划" sheetId="1" r:id="R4febfd27c4684dd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="执行规则" sheetId="2" r:id="R7579bb39257241c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目计划" sheetId="1" r:id="R4de1367cb66b4fa7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="执行规则" sheetId="2" r:id="Ra67d65289244481f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -632,7 +632,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="27" t="str">
-        <x:v>点选关窗器：11 天项目学习计划</x:v>
+        <x:v>窗口清理工具：开发与学习计划</x:v>
       </x:c>
       <x:c r="B1" s="28"/>
       <x:c r="C1" s="28"/>
@@ -643,7 +643,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="29" t="str">
-        <x:v>截止：2026年11月6日前。每天60分钟。核心代码由本人手写。</x:v>
+        <x:v>截止2026-11-06。每天100分钟，技术学习与软件交付同等重要，核心由本人独立编写。</x:v>
       </x:c>
       <x:c r="B2" s="28"/>
       <x:c r="C2" s="28"/>
@@ -675,7 +675,7 @@
         <x:v>自己手写的内容</x:v>
       </x:c>
       <x:c r="E4" s="31" t="str">
-        <x:v>当日验收</x:v>
+        <x:v>工程与学习验收</x:v>
       </x:c>
       <x:c r="F4" s="31" t="str">
         <x:v>完成状态</x:v>
@@ -689,61 +689,65 @@
         <x:v>2026-10-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B5" s="33" t="str">
-        <x:v>环境与鼠标坐标</x:v>
+        <x:v>环境与鼠标坐标（历史）</x:v>
       </x:c>
       <x:c r="C5" s="33" t="str">
-        <x:v>虚拟环境、导入模块、函数返回值、坐标元组</x:v>
+        <x:v>项目解释器、pywin32、坐标采样；已有基础不重教</x:v>
       </x:c>
       <x:c r="D5" s="34" t="str">
-        <x:v>安装 pywin32；编写读取并打印鼠标坐标的小实验</x:v>
+        <x:v>复用 practice_day01.py；保留已有坐标实验</x:v>
       </x:c>
       <x:c r="E5" s="35" t="str">
-        <x:v>程序运行成功；说明两个坐标数的含义</x:v>
+        <x:v>坐标移动对照与独立解释待实际记录</x:v>
       </x:c>
       <x:c r="F5" s="36" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="G5" s="36" t="str"/>
+        <x:v>已实现但未充分测试</x:v>
+      </x:c>
+      <x:c r="G5" s="36" t="str">
+        <x:v>已有坐标代码；仅静态/依赖证据，未收到移动对照结果。</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="86" customHeight="1">
       <x:c r="A6" s="37" t="d">
         <x:v>2026-10-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B6" s="38" t="str">
-        <x:v>识别鼠标所指窗口</x:v>
+        <x:v>定位原理与本人对照实验</x:v>
       </x:c>
       <x:c r="C6" s="38" t="str">
-        <x:v>窗口句柄、父子窗口、WindowFromPoint、GetAncestor</x:v>
+        <x:v>HWND、屏幕坐标、parent/owner、窗口层级与生命周期；消息仅有余力时预学</x:v>
       </x:c>
       <x:c r="D6" s="39" t="str">
-        <x:v>依据坐标识别顶层窗口，输出标题和句柄；只观察</x:v>
+        <x:v>本人设计三组对照与必要局部修改；工程和理解齐备且有余力再延伸关闭，不重写已有定位</x:v>
       </x:c>
       <x:c r="E6" s="40" t="str">
-        <x:v>指向两个普通窗口时识别结果不同；空标题不直接当错误</x:v>
+        <x:v>两窗/同窗两处有输出；本人说明点、句柄、根、参数与生命周期；对照有预测/结果/解释。</x:v>
       </x:c>
       <x:c r="F6" s="36" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="G6" s="36" t="str"/>
+        <x:v>已实现但未充分测试</x:v>
+      </x:c>
+      <x:c r="G6" s="36" t="str">
+        <x:v>现有定位代码语法通过，三组输出和独立解释待验证。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="86" customHeight="1">
       <x:c r="A7" s="32" t="d">
         <x:v>2026-10-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B7" s="33" t="str">
-        <x:v>验证关闭请求</x:v>
+        <x:v>稳定一次正常关闭请求</x:v>
       </x:c>
       <x:c r="C7" s="33" t="str">
-        <x:v>WM_CLOSE、PostMessage、错误处理；窗口与进程的区别</x:v>
+        <x:v>Windows 消息、生命周期、PostMessage/SendMessage、权限</x:v>
       </x:c>
       <x:c r="D7" s="34" t="str">
-        <x:v>对已确认的测试窗口发送正常关闭请求</x:v>
+        <x:v>对确认目标请求一次；处理查询/投递失败；完成依赖预检</x:v>
       </x:c>
       <x:c r="E7" s="35" t="str">
-        <x:v>空白测试窗口关闭；能解释请求不一定立即关闭；不结束进程</x:v>
+        <x:v>空白/未保存/取消有实测；能追踪消息投递与处理，解释参数、包装返回、权限和同步/异步取舍。</x:v>
       </x:c>
       <x:c r="F7" s="36" t="str">
-        <x:v>未开始</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="G7" s="36" t="str"/>
     </x:row>
@@ -752,19 +756,19 @@
         <x:v>2026-10-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B8" s="38" t="str">
-        <x:v>点选与取消：只识别</x:v>
+        <x:v>最小全局鼠标监听</x:v>
       </x:c>
       <x:c r="C8" s="38" t="str">
-        <x:v>全局输入事件、回调、清理状态、事件拦截</x:v>
+        <x:v>WH_MOUSE_LL、普通 GUI 事件区别、短回调、hook 生命周期</x:v>
       </x:c>
       <x:c r="D8" s="39" t="str">
-        <x:v>处理左键点选、右键或 Esc 取消；先只输出目标信息</x:v>
+        <x:v>先只识别；监听可启动/停止；验证封装候选</x:v>
       </x:c>
       <x:c r="E8" s="40" t="str">
-        <x:v>模式外点击正常；模式内点选不透传到目标；取消可用</x:v>
+        <x:v>普通输入正常、退出无遗留；独立启动/停止实验；能解释全局与 GUI 事件、短回调、传播和资源释放。</x:v>
       </x:c>
       <x:c r="F8" s="36" t="str">
-        <x:v>未开始</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="G8" s="36" t="str"/>
     </x:row>
@@ -773,19 +777,19 @@
         <x:v>2026-10-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B9" s="33" t="str">
-        <x:v>核心流程跑通</x:v>
+        <x:v>清理模式、取消与目标过滤</x:v>
       </x:c>
       <x:c r="C9" s="33" t="str">
-        <x:v>函数拆分、状态复位、窗口过滤</x:v>
+        <x:v>状态、输入配对、旧事件、过滤与资源复位</x:v>
       </x:c>
       <x:c r="D9" s="34" t="str">
-        <x:v>串起点选、过滤、关闭请求；一次点选后退出模式</x:v>
+        <x:v>开始后单次选择、过滤、请求、退出；Esc/右键取消</x:v>
       </x:c>
       <x:c r="E9" s="35" t="str">
-        <x:v>连续手动启动3次均可用；自身、桌面、任务栏不作为关闭目标</x:v>
+        <x:v>一次一请求、拒绝、取消、三轮通过；能解释状态/旧轮事件、输入配对、同步边界和模块责任。</x:v>
       </x:c>
       <x:c r="F9" s="36" t="str">
-        <x:v>未开始</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="G9" s="36" t="str"/>
     </x:row>
@@ -794,19 +798,19 @@
         <x:v>2026-10-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B10" s="38" t="str">
-        <x:v>接入最简界面</x:v>
+        <x:v>PySide6 基本主界面</x:v>
       </x:c>
       <x:c r="C10" s="38" t="str">
-        <x:v>PySide6 窗口、按钮、布局、信号与槽；GUI线程边界</x:v>
+        <x:v>QApplication/QWidget、按钮、布局、信号槽及版本组合</x:v>
       </x:c>
       <x:c r="D10" s="39" t="str">
-        <x:v>编写开始/取消按钮与状态显示；将监听结果交给UI线程</x:v>
+        <x:v>搭建开始/取消/状态反馈外壳，准备业务入口；最小 GUI 构建冒烟</x:v>
       </x:c>
       <x:c r="E10" s="40" t="str">
-        <x:v>按钮可控制模式，界面不中断；已有核心函数继续复用</x:v>
+        <x:v>基本 GUI 响应与构建冒烟；本人说明 QApplication/控件、事件循环、信号槽与回调调用时机。</x:v>
       </x:c>
       <x:c r="F10" s="36" t="str">
-        <x:v>未开始</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="G10" s="36" t="str"/>
     </x:row>
@@ -815,19 +819,19 @@
         <x:v>2026-11-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B11" s="33" t="str">
-        <x:v>光标反馈与恢复</x:v>
+        <x:v>GUI 接线与跨应用光标</x:v>
       </x:c>
       <x:c r="C11" s="33" t="str">
-        <x:v>应用内与系统光标的区别、资源恢复、异常退出清理</x:v>
+        <x:v>GUI 事件循环、主线程、跨线程通知、状态同步</x:v>
       </x:c>
       <x:c r="D11" s="34" t="str">
-        <x:v>实现可跨窗口识别的清理光标；取消/完成/退出均恢复</x:v>
+        <x:v>从 GUI 启动和结束清理；实现选择光标与取消/失败/退出恢复</x:v>
       </x:c>
       <x:c r="E11" s="35" t="str">
-        <x:v>在其他普通窗口上可看出清理模式；结束后光标恢复</x:v>
+        <x:v>自身过滤、取消/三轮及跨应用光标恢复；能追踪线程通知与界面更新，解释阻塞和恢复责任。</x:v>
       </x:c>
       <x:c r="F11" s="36" t="str">
-        <x:v>未开始</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="G11" s="36" t="str"/>
     </x:row>
@@ -836,19 +840,19 @@
         <x:v>2026-11-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B12" s="38" t="str">
-        <x:v>首次打包与手测</x:v>
+        <x:v>首个独立运行版本</x:v>
       </x:c>
       <x:c r="C12" s="38" t="str">
-        <x:v>PyInstaller 基础、依赖、日志、故障复现</x:v>
+        <x:v>PyInstaller、解释器与依赖、资源路径、构建区别</x:v>
       </x:c>
       <x:c r="D12" s="39" t="str">
-        <x:v>打包本机可运行版本；记录并修复核心问题</x:v>
+        <x:v>先生成完整 onedir 构建；记录资源/图标/版本；核对安装测试环境</x:v>
       </x:c>
       <x:c r="E12" s="40" t="str">
-        <x:v>打包程序可启动；点选、取消、恢复光标均验证</x:v>
+        <x:v>脱离源码/项目环境启动回归；能说明解释器/库/动态后端/资源如何进入构建及缺失时怎样定位。</x:v>
       </x:c>
       <x:c r="F12" s="36" t="str">
-        <x:v>未开始</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="G12" s="36" t="str"/>
     </x:row>
@@ -857,19 +861,19 @@
         <x:v>2026-11-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B13" s="33" t="str">
-        <x:v>缓冲与任务栏探索</x:v>
+        <x:v>必要交互与稳定性完善</x:v>
       </x:c>
       <x:c r="C13" s="33" t="str">
-        <x:v>仅在核心通过后研究任务栏按钮与窗口映射</x:v>
+        <x:v>轻量 QSS、图标、错误反馈、必要日志、回归测试</x:v>
       </x:c>
       <x:c r="D13" s="34" t="str">
-        <x:v>优先修复问题；有余力只做任务栏识别实验</x:v>
+        <x:v>修主要 Bug；清楚状态/错误提示；输出可安装的构建</x:v>
       </x:c>
       <x:c r="E13" s="35" t="str">
-        <x:v>任务栏支持是可选项；不能可靠匹配时不发送关闭请求</x:v>
+        <x:v>主要 Bug 复现→本人修改→复测；能讲原因/参数/流程/局限；无故障不编造，暂停低价值扩展。</x:v>
       </x:c>
       <x:c r="F13" s="36" t="str">
-        <x:v>未开始</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="G13" s="36" t="str"/>
     </x:row>
@@ -878,19 +882,19 @@
         <x:v>2026-11-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B14" s="38" t="str">
-        <x:v>冻结功能与整理交付</x:v>
+        <x:v>安装包与工程交付</x:v>
       </x:c>
       <x:c r="C14" s="38" t="str">
-        <x:v>回归检查、依赖说明、Git 提交、README</x:v>
+        <x:v>Inno Setup、安装/卸载、快捷方式、README、发布</x:v>
       </x:c>
       <x:c r="D14" s="39" t="str">
-        <x:v>不加新功能；完善UI提示；重打包；写运行与限制说明</x:v>
+        <x:v>制作安装包和卸载入口，完善运行说明与交付文件清单</x:v>
       </x:c>
       <x:c r="E14" s="40" t="str">
-        <x:v>源码与可运行版本对应；说明AI参与范围</x:v>
+        <x:v>安装→启动→核心回归→退出→卸载有结果；能解释 exe/安装器、版本、快捷方式与数据保留。</x:v>
       </x:c>
       <x:c r="F14" s="36" t="str">
-        <x:v>未开始</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="G14" s="36" t="str"/>
     </x:row>
@@ -899,30 +903,54 @@
         <x:v>2026-11-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B15" s="33" t="str">
-        <x:v>最终验收与独立讲解</x:v>
+        <x:v>候选版冻结与技术复盘</x:v>
       </x:c>
       <x:c r="C15" s="33" t="str">
-        <x:v>复盘调用流程；独立修改小需求</x:v>
+        <x:v>实际架构、API 参数、选型、真实排障与已知限制</x:v>
       </x:c>
       <x:c r="D15" s="34" t="str">
-        <x:v>验证常见场景；不用参考讲解关键代码；整理成品</x:v>
+        <x:v>形成可演示候选交付版；整理真实成长证据与项目介绍</x:v>
       </x:c>
       <x:c r="E15" s="35" t="str">
-        <x:v>11月6日前交付；能解释坐标、句柄、关闭请求、监听与退出流程</x:v>
+        <x:v>候选成品复验和源码对应；本人能用实际代码/实验解释核心机制、选型、参数、真实排障与限制。</x:v>
       </x:c>
       <x:c r="F15" s="36" t="str">
-        <x:v>未开始</x:v>
+        <x:v>尚未开始</x:v>
       </x:c>
       <x:c r="G15" s="36" t="str"/>
+    </x:row>
+    <x:row r="16" ht="86" customHeight="1">
+      <x:c r="A16" s="37" t="d">
+        <x:v>2026-11-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B16" s="38" t="str">
+        <x:v>最终验收与交付</x:v>
+      </x:c>
+      <x:c r="C16" s="38" t="str">
+        <x:v>只复用已学技术，不安排重大新功能</x:v>
+      </x:c>
+      <x:c r="D16" s="39" t="str">
+        <x:v>最终回归、必要小修、成果提交及版本核对</x:v>
+      </x:c>
+      <x:c r="E16" s="40" t="str">
+        <x:v>最终成品与安装卸载证据齐全；工程和学习缺项分记，保留版本/提交与本人讲解，不假称掌握。</x:v>
+      </x:c>
+      <x:c r="F16" s="36" t="str">
+        <x:v>尚未开始</x:v>
+      </x:c>
+      <x:c r="G16" s="36"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:D1"/>
     <x:mergeCell ref="A2:D2"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="F5:F15">
-      <x:formula1>"未开始,进行中,已完成,待解决"</x:formula1>
+      <x:formula1>"已完成并验证,已实现但未充分测试,正在开发,尚未开始,暂缓或取消"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F16">
+      <x:formula1>"已完成并验证,已实现但未充分测试,正在开发,尚未开始,暂缓或取消"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -950,7 +978,7 @@
         <x:v>首要目标</x:v>
       </x:c>
       <x:c r="B2" s="40" t="str">
-        <x:v>2026年11月6日前交付Windows桌面点选关窗工具。每天60分钟。</x:v>
+        <x:v>2026-11-06 前独立交付可安装、可运行的 Windows GUI 软件，并真正学会关键新技术；学习与交付同等重要，两者须有真实证据。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="43" customHeight="1">
@@ -958,7 +986,7 @@
         <x:v>核心行为</x:v>
       </x:c>
       <x:c r="B3" s="35" t="str">
-        <x:v>开始清理后左键点选一个普通窗口，发送正常关闭请求，随后退出清理模式。右键或Esc取消。一次一窗是第一版建议。</x:v>
+        <x:v>开始清理后光标变化；左键选择普通窗口，过滤后投递一次正常关闭请求并退出。Esc/右键取消；再点开始可继续。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="43" customHeight="1">
@@ -966,7 +994,7 @@
         <x:v>本人负责</x:v>
       </x:c>
       <x:c r="B4" s="40" t="str">
-        <x:v>需求、算法与流程、窗口识别、关闭请求、监听和取消、状态、过滤、接线、排错与打包均由本人亲手完成并能解释。</x:v>
+        <x:v>本人独立完成识别、请求、监听/拦截、取消、状态、过滤及核心接线，并能解释。参考使用、修改和验证如实记录。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="43" customHeight="1">
@@ -974,7 +1002,7 @@
         <x:v>AI可协助</x:v>
       </x:c>
       <x:c r="B5" s="35" t="str">
-        <x:v>解答概念与报错、推荐资料、提出验证思路、优化界面视觉。核心实现先由本人尝试，AI不直接提供整段答案。</x:v>
+        <x:v>讲解、查资料、局部独立示例、调试方向、审查与 UI 优化；具体授权内可协助资源/构建配置，不代写核心。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="43" customHeight="1">
@@ -982,7 +1010,7 @@
         <x:v>按需学习</x:v>
       </x:c>
       <x:c r="B6" s="40" t="str">
-        <x:v>每天5分钟回忆、15分钟阅读理解、30分钟手写实验、10分钟验证与记录。安装排错也计入学习时间。</x:v>
+        <x:v>默认：新技术/原理30、独立编码实验调试50、测试10、技术总结/Git/面试10分钟；也可25+55+10+10，总计100分钟。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="43" customHeight="1">
@@ -990,7 +1018,7 @@
         <x:v>范围</x:v>
       </x:c>
       <x:c r="B7" s="35" t="str">
-        <x:v>主窗口、开始/取消、光标反馈、点选普通窗口、必要过滤、打包。无需数据库、登录或为了凑功能保存数据。</x:v>
+        <x:v>基本 GUI、开始/取消、跨应用选择光标、正常关闭、必要过滤/错误恢复、独立构建及安装卸载。数据库、登录、复杂设置不纳入 MVP。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="43" customHeight="1">
@@ -1003,10 +1031,10 @@
     </x:row>
     <x:row r="9" ht="43" customHeight="1">
       <x:c r="A9" s="35" t="str">
-        <x:v>两个检查点</x:v>
+        <x:v>交付检查点</x:v>
       </x:c>
       <x:c r="B9" s="35" t="str">
-        <x:v>10月30日：核心流程。11月2日：首次打包。落后时用11月3日缓冲；先去掉任务栏探索与UI装饰。</x:v>
+        <x:v>10-28 识别/请求；10-30 输入核心；11-01 GUI/光标；11-02 独立构建；11-04 安装卸载；11-05 候选冻结；11-06 最终交付。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="43" customHeight="1">
@@ -1014,7 +1042,7 @@
         <x:v>卡住如何求助</x:v>
       </x:c>
       <x:c r="B10" s="40" t="str">
-        <x:v>给出预期行为、实际行为、自己写的最小代码、完整报错和已尝试的方法。先请求解释与提示。</x:v>
+        <x:v>提供代码、预期、实际结果、完整报错和已试方法；定位→原理→思路→必要局部示例→本人修改→审查复测。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="43" customHeight="1">
@@ -1030,23 +1058,23 @@
         <x:v>学习证据</x:v>
       </x:c>
       <x:c r="B12" s="40" t="str">
-        <x:v>每天留下自己写的小实验，并记录：今天解决的问题、一个失败及原因、能解释的关键函数。</x:v>
+        <x:v>每阶段同时记录工程成果（功能/源码/测试/Git）和学习成果（原理/本人实验/选型/参数流程/真实排障/讲解）；不能只会调用或只背概念。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="43" customHeight="1">
       <x:c r="A13" s="35" t="str">
-        <x:v>今天60分钟</x:v>
+        <x:v>每日100分钟</x:v>
       </x:c>
       <x:c r="B13" s="35" t="str">
-        <x:v>0–10分钟建环境；10–25分钟理解模块、函数与返回值；25–50分钟自己写坐标实验；50–60分钟移动鼠标验证并记录。</x:v>
+        <x:v>每天100分钟：30分钟关键原理、50分钟本人编码实验、10分钟测试、10分钟双类总结；时间冲突先减扩展，不先砍核心技术学习。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="43" customHeight="1">
       <x:c r="A14" s="40" t="str">
-        <x:v>今天交付</x:v>
+        <x:v>当前开发起点</x:v>
       </x:c>
       <x:c r="B14" s="40" t="str">
-        <x:v>一个本人手写的day01_cursor.py。运行后打印坐标；能解释坐标元组；安装失败则保留完整报错先解决环境。</x:v>
+        <x:v>先学 HWND/坐标/窗口层级，再用现有定位代码做本人预测与对照；定位运行和理解齐备后有余力才延伸关闭，稳定请求仍在10-28完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="43" customHeight="1">
@@ -1103,6 +1131,70 @@
       </x:c>
       <x:c r="B21" s="35" t="str">
         <x:v>https://doc.qt.io/qtforpython-6/deployment/deployment-pyinstaller.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="43" customHeight="1">
+      <x:c r="A22" s="40" t="str">
+        <x:v>优先技术</x:v>
+      </x:c>
+      <x:c r="B22" s="40" t="str">
+        <x:v>Python、pywin32/Windows API、Windows 输入机制、PySide6/Qt、QSS、Git、PyInstaller、Inno Setup。候选封装须实测。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="43" customHeight="1">
+      <x:c r="A23" s="35" t="str">
+        <x:v>面试复盘</x:v>
+      </x:c>
+      <x:c r="B23" s="35" t="str">
+        <x:v>每天围绕真实内容共约3～5题，题目集中列出，答案统一文末；不强制逐题互动，不为面试堆技术名词。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="43" customHeight="1">
+      <x:c r="A24" s="40" t="str">
+        <x:v>范围缩减</x:v>
+      </x:c>
+      <x:c r="B24" s="40" t="str">
+        <x:v>P0/P1/P2 是功能优先级，不是压低学习地位。先砍托盘、动画、高级设置、精修和重复实现；保留核心原理、本人实验、安全与发布验证。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="43" customHeight="1">
+      <x:c r="A25" s="35" t="str">
+        <x:v>五类进度状态</x:v>
+      </x:c>
+      <x:c r="B25" s="35" t="str">
+        <x:v>已完成并验证；已实现但未充分测试；正在开发；尚未开始；暂缓或取消。依据证据填写，不因日期过去自动完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="43" customHeight="1">
+      <x:c r="A26" s="40" t="str">
+        <x:v>Git 与成果记录</x:v>
+      </x:c>
+      <x:c r="B26" s="40" t="str">
+        <x:v>用户亲手检查忽略规则、差异、暂存、commit、push 并核对 GitHub。源码、测试和真实排障关联提交；保存不等于提交或推送。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="43" customHeight="1">
+      <x:c r="A27" s="35" t="str">
+        <x:v>当前计划来源</x:v>
+      </x:c>
+      <x:c r="B27" s="35" t="str">
+        <x:v>docs/development-plan.md；新日执行单在 docs/learning/dayXX.md；真实成长记录在 docs/interview/。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="43" customHeight="1">
+      <x:c r="A28" s="40" t="str">
+        <x:v>五层技术深度</x:v>
+      </x:c>
+      <x:c r="B28" s="40" t="str">
+        <x:v>是什么、为什么、怎么工作、怎么使用、怎么应用与改进；API 参数/返回/异常与本人实验对应，不以普通 Python 复习冒充新技术。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="43" customHeight="1">
+      <x:c r="A29" s="35" t="str">
+        <x:v>掌握与证据</x:v>
+      </x:c>
+      <x:c r="B29" s="35" t="str">
+        <x:v>理解原理→独立编写→实际测试→排查问题→能够讲解。缺一环标待补；没有真实故障可做标注的边界分析，不编造修复经历。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
